--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18 11:03</t>
+    <t xml:space="preserve">2026-09-06 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
